--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A603C4-551B-4641-84A8-4AB6B9C002FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97813DA9-5455-4B4D-88B3-FF5E1DAB5974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>Nazwa</t>
   </si>
@@ -189,22 +189,53 @@
     <t>PolardbX</t>
   </si>
   <si>
-    <t>python / kubernetes</t>
-  </si>
-  <si>
     <t>https://github.com/polardb/polardbx</t>
   </si>
   <si>
     <t>SingleStore</t>
   </si>
   <si>
-    <t>kubernetes</t>
-  </si>
-  <si>
     <t>Crate</t>
   </si>
   <si>
     <t>https://github.com/crate/crate</t>
+  </si>
+  <si>
+    <t>nie ma?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>python</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / kubernetes (hive)</t>
+    </r>
+  </si>
+  <si>
+    <t>Docker  (local)</t>
+  </si>
+  <si>
+    <t>5,7,32</t>
+  </si>
+  <si>
+    <t>uruchomiony</t>
+  </si>
+  <si>
+    <t>6,2,2</t>
   </si>
 </sst>
 </file>
@@ -212,9 +243,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,8 +253,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +286,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -255,14 +305,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,42 +878,57 @@
       <c r="A14" t="s">
         <v>53</v>
       </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
         <v>54</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="1048575" spans="1:1" x14ac:dyDescent="0.35">

--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97813DA9-5455-4B4D-88B3-FF5E1DAB5974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BD3022-D3FB-4529-A52F-A27C6A8FF0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>Nazwa</t>
   </si>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t>6,2,2</t>
+  </si>
+  <si>
+    <t>Host=localhost;Port=3366;Username=root;Password=password;AllowUserVariables=True;</t>
+  </si>
+  <si>
+    <t>Host=localhost;Port=5434;Username=crate;Include Error Detail=true</t>
+  </si>
+  <si>
+    <t>Host=hive;Port=56750;Username=polardbx_root;Password=jtGglNHV;AllowUserVariables=True;</t>
   </si>
 </sst>
 </file>
@@ -893,6 +902,9 @@
       <c r="G14" t="s">
         <v>54</v>
       </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -913,6 +925,9 @@
       <c r="G15" t="s">
         <v>58</v>
       </c>
+      <c r="H15" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -929,6 +944,9 @@
       </c>
       <c r="G16" t="s">
         <v>57</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="1048575" spans="1:1" x14ac:dyDescent="0.35">

--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BD3022-D3FB-4529-A52F-A27C6A8FF0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E17B1-0EF4-433B-BD19-F2651C7FF700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>Nazwa</t>
   </si>
@@ -87,9 +87,6 @@
     <t>tak</t>
   </si>
   <si>
-    <t>nie</t>
-  </si>
-  <si>
     <t>nie udało się</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
   </si>
   <si>
     <t>Postgresql/MySQL</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>https://github.com/apache/shardingsphere</t>
@@ -245,6 +239,12 @@
   </si>
   <si>
     <t>Host=hive;Port=56750;Username=polardbx_root;Password=jtGglNHV;AllowUserVariables=True;</t>
+  </si>
+  <si>
+    <t>Kubernetes (local)</t>
+  </si>
+  <si>
+    <t>uruchomiony (tylko mysql)</t>
   </si>
 </sst>
 </file>
@@ -611,10 +611,10 @@
     <col min="2" max="2" width="16.36328125" customWidth="1"/>
     <col min="3" max="3" width="19.6328125" customWidth="1"/>
     <col min="4" max="4" width="27.36328125" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" customWidth="1"/>
     <col min="6" max="6" width="15.1796875" customWidth="1"/>
     <col min="7" max="7" width="39.7265625" customWidth="1"/>
-    <col min="8" max="8" width="73" customWidth="1"/>
+    <col min="8" max="8" width="92.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -637,10 +637,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -654,16 +654,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -677,13 +677,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -700,7 +700,7 @@
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -714,16 +714,16 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -737,16 +737,16 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -766,10 +766,10 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -789,10 +789,10 @@
         <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -806,16 +806,16 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -823,69 +823,72 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
         <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
         <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -894,59 +897,59 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
         <v>62</v>
-      </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1048575" spans="1:1" x14ac:dyDescent="0.35">

--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E17B1-0EF4-433B-BD19-F2651C7FF700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46679EA2-DC36-4990-85F7-BD723BCD377B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>Nazwa</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>uruchomiony (tylko mysql)</t>
+  </si>
+  <si>
+    <t>Docker (local)</t>
   </si>
 </sst>
 </file>
@@ -942,6 +945,9 @@
       <c r="C16" t="s">
         <v>5</v>
       </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
       <c r="E16" s="7" t="s">
         <v>60</v>
       </c>

--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46679EA2-DC36-4990-85F7-BD723BCD377B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0D4C20-8DFE-4323-9706-11F21EF3254D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>Nazwa</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Docker (local)</t>
+  </si>
+  <si>
+    <t>Firma</t>
   </si>
 </sst>
 </file>
@@ -317,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -327,6 +330,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,20 +612,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1048575"/>
+  <dimension ref="A1:I1048575"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" customWidth="1"/>
     <col min="2" max="2" width="16.36328125" customWidth="1"/>
     <col min="3" max="3" width="19.6328125" customWidth="1"/>
     <col min="4" max="4" width="27.36328125" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="6" max="6" width="15.1796875" customWidth="1"/>
-    <col min="7" max="7" width="39.7265625" customWidth="1"/>
-    <col min="8" max="8" width="92.81640625" customWidth="1"/>
+    <col min="5" max="6" width="25.7265625" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="8" max="8" width="39.7265625" customWidth="1"/>
+    <col min="9" max="9" width="92.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,17 +641,20 @@
       <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -662,14 +670,15 @@
       <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="9"/>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -685,11 +694,12 @@
       <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="F3" s="9"/>
+      <c r="I3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -702,11 +712,12 @@
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F4" s="9"/>
+      <c r="I4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -722,14 +733,15 @@
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" s="9"/>
+      <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -745,14 +757,15 @@
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" s="9"/>
+      <c r="H6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -768,14 +781,15 @@
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G7" t="s">
+      <c r="F7" s="9"/>
+      <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -791,14 +805,15 @@
       <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" s="9"/>
+      <c r="H8" t="s">
         <v>27</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -814,14 +829,15 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="G9" t="s">
+      <c r="F9" s="9"/>
+      <c r="H9" t="s">
         <v>28</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -831,11 +847,12 @@
       <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F10" s="9"/>
+      <c r="H10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -851,14 +868,15 @@
       <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F11" s="9"/>
+      <c r="H11" t="s">
         <v>38</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -868,11 +886,12 @@
       <c r="E12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G12" t="s">
+      <c r="F12" s="10"/>
+      <c r="H12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -885,11 +904,12 @@
       <c r="E13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G13" t="s">
+      <c r="F13" s="10"/>
+      <c r="H13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -905,14 +925,15 @@
       <c r="E14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" s="10"/>
+      <c r="H14" t="s">
         <v>52</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -928,14 +949,15 @@
       <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G15" t="s">
+      <c r="F15" s="9"/>
+      <c r="H15" t="s">
         <v>56</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -951,10 +973,11 @@
       <c r="E16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F16" s="9"/>
+      <c r="H16" t="s">
         <v>55</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>63</v>
       </c>
     </row>

--- a/DistributedDbs.xlsx
+++ b/DistributedDbs.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Studia\Praca-Magisterka-Distributed-Sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0D4C20-8DFE-4323-9706-11F21EF3254D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96603334-DAAF-452F-9949-6701C3E7A6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -320,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -330,8 +331,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,7 +641,7 @@
       <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" t="s">
         <v>68</v>
       </c>
       <c r="G1" t="s">
@@ -670,7 +670,6 @@
       <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="9"/>
       <c r="H2" t="s">
         <v>23</v>
       </c>
@@ -694,7 +693,6 @@
       <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="9"/>
       <c r="I3" t="s">
         <v>39</v>
       </c>
@@ -712,7 +710,6 @@
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9"/>
       <c r="I4" t="s">
         <v>45</v>
       </c>
@@ -733,7 +730,6 @@
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9"/>
       <c r="H5" t="s">
         <v>24</v>
       </c>
@@ -757,7 +753,6 @@
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="9"/>
       <c r="H6" t="s">
         <v>25</v>
       </c>
@@ -781,7 +776,6 @@
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="9"/>
       <c r="H7" t="s">
         <v>26</v>
       </c>
@@ -805,7 +799,6 @@
       <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="9"/>
       <c r="H8" t="s">
         <v>27</v>
       </c>
@@ -829,7 +822,6 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="9"/>
       <c r="H9" t="s">
         <v>28</v>
       </c>
@@ -847,7 +839,6 @@
       <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="9"/>
       <c r="H10" t="s">
         <v>29</v>
       </c>
@@ -868,7 +859,6 @@
       <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="9"/>
       <c r="H11" t="s">
         <v>38</v>
       </c>
@@ -886,7 +876,7 @@
       <c r="E12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="9"/>
       <c r="H12" t="s">
         <v>47</v>
       </c>
@@ -904,7 +894,7 @@
       <c r="E13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="9"/>
       <c r="H13" t="s">
         <v>50</v>
       </c>
@@ -925,7 +915,7 @@
       <c r="E14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="9"/>
       <c r="H14" t="s">
         <v>52</v>
       </c>
@@ -949,7 +939,6 @@
       <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="9"/>
       <c r="H15" t="s">
         <v>56</v>
       </c>
@@ -973,7 +962,6 @@
       <c r="E16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="9"/>
       <c r="H16" t="s">
         <v>55</v>
       </c>
@@ -988,4 +976,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73738F3-53E9-49F2-920A-F68124CB6172}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>